--- a/static/files/Product_Template.xlsx
+++ b/static/files/Product_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B9E041-31B5-4F6F-8F0A-525812C600B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0B3B7A-0D39-442A-A9DA-857D9CA99F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,19 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>P001</t>
-  </si>
-  <si>
-    <t>Grocery</t>
-  </si>
-  <si>
-    <t>Rice Bag 10kg</t>
-  </si>
-  <si>
-    <t>Premium basmati rice 10kg</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Description</t>
   </si>
@@ -443,56 +431,40 @@
   <sheetData>
     <row r="1" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>450</v>
-      </c>
-      <c r="F2" s="7">
-        <v>520</v>
-      </c>
-      <c r="G2" s="7">
-        <v>50</v>
-      </c>
-      <c r="H2" s="8">
-        <v>46387</v>
-      </c>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
